--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bansal_s\PyCharmMiscProject\Day 36\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh\PycharmProjects\scheduled-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D41080E-6A05-46A0-86AB-36BF90A0ADE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B67D93-8AB1-4050-8C91-2C8C97B6C73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DBF5B9E9-41A4-47B0-865D-D7F003C09541}"/>
   </bookViews>
@@ -612,7 +612,7 @@
         <v>172.81013157894733</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>42</v>
@@ -631,7 +631,7 @@
         <v>503.69607032558139</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>42</v>
@@ -650,7 +650,7 @@
         <v>57.830406026058633</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>42</v>
@@ -669,7 +669,7 @@
         <v>110.19422105670104</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>42</v>
@@ -688,7 +688,7 @@
         <v>554.99766666666665</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>42</v>
@@ -707,7 +707,7 @@
         <v>167.3698870779221</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>42</v>
@@ -726,7 +726,7 @@
         <v>26.013505000000002</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>42</v>
@@ -764,7 +764,7 @@
         <v>23.33278516426159</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>42</v>
@@ -783,7 +783,7 @@
         <v>177.50579930069932</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>42</v>
@@ -802,7 +802,7 @@
         <v>104.72509670487105</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>42</v>
@@ -821,7 +821,7 @@
         <v>659.84090909090912</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>42</v>
@@ -840,7 +840,7 @@
         <v>119.79999999999998</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>42</v>
@@ -859,7 +859,7 @@
         <v>717.05555555555554</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>42</v>
@@ -878,7 +878,7 @@
         <v>44.493333333333332</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>42</v>
@@ -897,7 +897,7 @@
         <v>193</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>42</v>
@@ -916,7 +916,7 @@
         <v>155.83000000000001</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>42</v>
@@ -935,7 +935,7 @@
         <v>415</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>42</v>
@@ -954,7 +954,7 @@
         <v>2165</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>42</v>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh\PycharmProjects\scheduled-tasks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bansal_s\PyCharmMiscProject\scheduled-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B67D93-8AB1-4050-8C91-2C8C97B6C73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34150D89-BD06-47DC-8E19-DC8084185601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DBF5B9E9-41A4-47B0-865D-D7F003C09541}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Name</t>
   </si>
@@ -50,117 +50,12 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Bharat Dynamics</t>
-  </si>
-  <si>
-    <t>CAMS</t>
-  </si>
-  <si>
-    <t>Bharat Electronics</t>
-  </si>
-  <si>
-    <t>Indian Hotels</t>
-  </si>
-  <si>
-    <t>United Spirits</t>
-  </si>
-  <si>
-    <t>ITC</t>
-  </si>
-  <si>
-    <t>ITC Hotels</t>
-  </si>
-  <si>
-    <t>Yes Bank</t>
-  </si>
-  <si>
-    <t>IRFC</t>
-  </si>
-  <si>
-    <t>Exide</t>
-  </si>
-  <si>
-    <t>DLINK</t>
-  </si>
-  <si>
-    <t>Amara Raj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazagon Dock </t>
-  </si>
-  <si>
-    <t>Adani Ports</t>
-  </si>
-  <si>
-    <t>HUDCO</t>
-  </si>
-  <si>
-    <t>Tata Power</t>
-  </si>
-  <si>
-    <t>India Grid</t>
-  </si>
-  <si>
-    <t>Mind Space</t>
-  </si>
-  <si>
     <t>ICICI Pru AMC</t>
   </si>
   <si>
-    <t>DLINKINDIA.BO</t>
-  </si>
-  <si>
-    <t>ARE&amp;M.BO</t>
-  </si>
-  <si>
-    <t>MAZDOCK.BO</t>
-  </si>
-  <si>
-    <t>ADANIPORTS.BO</t>
-  </si>
-  <si>
-    <t>HUDCO.BO</t>
-  </si>
-  <si>
-    <t>TATAPOWER.BO</t>
-  </si>
-  <si>
-    <t>INDIGRID.BO</t>
-  </si>
-  <si>
-    <t>MINDSPACE.BO</t>
-  </si>
-  <si>
     <t>ICICIAMC.BO</t>
   </si>
   <si>
-    <t>BDL.BO</t>
-  </si>
-  <si>
-    <t>CAMS.BO</t>
-  </si>
-  <si>
-    <t>BEL.BO</t>
-  </si>
-  <si>
-    <t>INDHOTEL.BO</t>
-  </si>
-  <si>
-    <t>UNITDSPR.BO</t>
-  </si>
-  <si>
-    <t>ITC.BO</t>
-  </si>
-  <si>
-    <t>ITCHOTELS.BO</t>
-  </si>
-  <si>
-    <t>IRFC.BO</t>
-  </si>
-  <si>
-    <t>EXIDEIND.BO</t>
-  </si>
-  <si>
     <t>Symbol</t>
   </si>
   <si>
@@ -177,9 +72,6 @@
   </si>
   <si>
     <t>Check</t>
-  </si>
-  <si>
-    <t>YESBANK.BO</t>
   </si>
 </sst>
 </file>
@@ -570,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FCA83A5-EE17-4E29-B37F-BCB7A5AAA969}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -583,19 +475,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -606,361 +498,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>172.81013157894733</v>
+        <v>2165</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3">
-        <v>503.69607032558139</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="3">
-        <v>57.830406026058633</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3">
-        <v>110.19422105670104</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="3">
-        <v>554.99766666666665</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="3">
-        <v>167.3698870779221</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="3">
-        <v>26.013505000000002</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3">
-        <v>12.176151673185572</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3">
-        <v>23.33278516426159</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3">
-        <v>177.50579930069932</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="3">
-        <v>104.72509670487105</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="3">
-        <v>659.84090909090912</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3">
-        <v>119.79999999999998</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
-        <v>717.05555555555554</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="3">
-        <v>44.493333333333332</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="3">
-        <v>193</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="3">
-        <v>155.83000000000001</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="3">
-        <v>415</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="3">
-        <v>2165</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bansal_s\PyCharmMiscProject\scheduled-tasks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suresh\PycharmProjects\scheduled-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34150D89-BD06-47DC-8E19-DC8084185601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B67D93-8AB1-4050-8C91-2C8C97B6C73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DBF5B9E9-41A4-47B0-865D-D7F003C09541}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
@@ -50,12 +50,117 @@
     <t>Value</t>
   </si>
   <si>
+    <t>Bharat Dynamics</t>
+  </si>
+  <si>
+    <t>CAMS</t>
+  </si>
+  <si>
+    <t>Bharat Electronics</t>
+  </si>
+  <si>
+    <t>Indian Hotels</t>
+  </si>
+  <si>
+    <t>United Spirits</t>
+  </si>
+  <si>
+    <t>ITC</t>
+  </si>
+  <si>
+    <t>ITC Hotels</t>
+  </si>
+  <si>
+    <t>Yes Bank</t>
+  </si>
+  <si>
+    <t>IRFC</t>
+  </si>
+  <si>
+    <t>Exide</t>
+  </si>
+  <si>
+    <t>DLINK</t>
+  </si>
+  <si>
+    <t>Amara Raj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazagon Dock </t>
+  </si>
+  <si>
+    <t>Adani Ports</t>
+  </si>
+  <si>
+    <t>HUDCO</t>
+  </si>
+  <si>
+    <t>Tata Power</t>
+  </si>
+  <si>
+    <t>India Grid</t>
+  </si>
+  <si>
+    <t>Mind Space</t>
+  </si>
+  <si>
     <t>ICICI Pru AMC</t>
   </si>
   <si>
+    <t>DLINKINDIA.BO</t>
+  </si>
+  <si>
+    <t>ARE&amp;M.BO</t>
+  </si>
+  <si>
+    <t>MAZDOCK.BO</t>
+  </si>
+  <si>
+    <t>ADANIPORTS.BO</t>
+  </si>
+  <si>
+    <t>HUDCO.BO</t>
+  </si>
+  <si>
+    <t>TATAPOWER.BO</t>
+  </si>
+  <si>
+    <t>INDIGRID.BO</t>
+  </si>
+  <si>
+    <t>MINDSPACE.BO</t>
+  </si>
+  <si>
     <t>ICICIAMC.BO</t>
   </si>
   <si>
+    <t>BDL.BO</t>
+  </si>
+  <si>
+    <t>CAMS.BO</t>
+  </si>
+  <si>
+    <t>BEL.BO</t>
+  </si>
+  <si>
+    <t>INDHOTEL.BO</t>
+  </si>
+  <si>
+    <t>UNITDSPR.BO</t>
+  </si>
+  <si>
+    <t>ITC.BO</t>
+  </si>
+  <si>
+    <t>ITCHOTELS.BO</t>
+  </si>
+  <si>
+    <t>IRFC.BO</t>
+  </si>
+  <si>
+    <t>EXIDEIND.BO</t>
+  </si>
+  <si>
     <t>Symbol</t>
   </si>
   <si>
@@ -72,6 +177,9 @@
   </si>
   <si>
     <t>Check</t>
+  </si>
+  <si>
+    <t>YESBANK.BO</t>
   </si>
 </sst>
 </file>
@@ -462,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FCA83A5-EE17-4E29-B37F-BCB7A5AAA969}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -475,19 +583,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
@@ -498,19 +606,361 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3">
-        <v>2165</v>
+        <v>172.81013157894733</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3">
+        <v>503.69607032558139</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3">
+        <v>57.830406026058633</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3">
+        <v>110.19422105670104</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3">
+        <v>554.99766666666665</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="3">
+        <v>167.3698870779221</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3">
+        <v>26.013505000000002</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12.176151673185572</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3">
+        <v>23.33278516426159</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="3">
+        <v>177.50579930069932</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3">
+        <v>104.72509670487105</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3">
+        <v>659.84090909090912</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3">
+        <v>119.79999999999998</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3">
+        <v>717.05555555555554</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3">
+        <v>44.493333333333332</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3">
+        <v>193</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3">
+        <v>155.83000000000001</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3">
+        <v>415</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2165</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
